--- a/resume_parsed.xlsx
+++ b/resume_parsed.xlsx
@@ -70,49 +70,49 @@
     <t>Aman_SDE_Fresher-2.pdf</t>
   </si>
   <si>
-    <t>{"name": "Tanisha Kumari", "email": "tanishak2266@gmail.com", "phone": "+91 9608954838", "college": "Indian Institute of Technology (IIT) Bombay", "skills": ["Data Science", "Numpy", "Matplotlib", "MATLAB", "PyTorch", "Pandas", "NLTK", "SQL", "PostgreSQL", "PowerBI", "TensorFlow", "OpenCV"], "graduation_year": 2025, "certification": ["Machine Learning: Unsupervised Learning Recommenders and Reinforcement Learning", "Supervised Machine Learning: Regression and Classifications", "Advanced learning algorithm", "Excel: Excel Skills for Business: Essentials", "Excel: Excel Skills for Business: Intermediate I", "Excel: Excel Skills for Business: Intermediate II", "Excel: Excel Skills for Business: Advanced"], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["Operations Intern", "Data Analyst Intern"], "durations": ["Jan\u201925 - ongoing", "Jun\u201924 - Jul\u201924"], "companies": ["Freedom with AI", "NoQs Digital"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Tanisha_ Kumari.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Shivam Mane", "email": "shivam.27mane@gmail.com", "phone": "+91 9175791024", "college": "Sanjay Ghodawat Institute Kolhapur", "skills": ["Angular", "AWS", "JavaScript", "TypeScript", "PHP", "Bootstrap", "CodeIgniter", "HTML &amp; CSS"], "graduation_year": 2020, "certification": [], "experience": 3, "Intern_Experience": {"duration_months": 3, "roles": ["Frontend Web Developer - Intern"], "durations": ["2 months", "3 months"], "companies": ["SRV Media Pvt. Ltd"], "locations": ["onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Shivam-Mane-Resume-March-2025.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Rupali Chavare", "email": "rupalichavare6@gmail.com", "phone": "9834244346", "college": "Bharati Vidyapeeth University", "skills": ["Java", "Web development", "ReactJS", "Spring Boot", "Hibernate", "SQL", "JavaScript", "Angular"], "graduation_year": 2025, "certification": ["SEED Certified"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Software Development Intern"], "durations": ["6 months"], "companies": ["Codeseed"], "locations": ["Pandharpur, India"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\RupaliChavare_Cv.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "AJAY KUSHWAHA", "email": "ajayindial925@gmail.com", "phone": "+91 8932012815", "college": "KIET Group of Institutions (Affiliated to AKTU University)", "skills": ["Java", "Python", "SQL", "HTML", "CSS", "JavaScript", "RestAPI", "SpringBoot", "Django", "VS Code", "Eclipse", "GitHub", "Postman", "Data Structures and Algorithms", "Object-Oriented Programming", "Operating Systems", "Database Management Systems", "MySQL"], "graduation_year": 2024, "certification": ["Java by Coding Ninjas", "Python Programming and Machine Learning", "API Developer (Python/Django Rest/Flask/PostgreSQL/Postman)"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Frontend Developer Intern", "Java Developer Intern"], "durations": ["3 months", "4 months"], "companies": ["IBM SkillsBuild", "Wipro Limited"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\resume_AjayKushwaha.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Omkar Shirpure", "email": "22b0910@iitb.ac.in", "phone": "null", "college": "Indian Institute of Technology Bombay", "skills": ["C/C++", "Python", "Go", "Scala", "Haskell", "Lisp", "Bash", "x86 and MIPS Assembly", "VHDL", "DART", "Verilog", "React", "Next.js", "Flutter", "Node.js", "Django", "MongoDB", "PostgreSQL", "Angular", "Excel", "NumPy", "Pandas", "MatPlotLib", "SciPy", "PyTorch", "TensorFlow", "scikit-learn", "Kubernetes", "Docker", "Redis", "ELK Stack", "HiveDB", "MATLAB", "Git", "Sed", "Awk", "GDB"], "graduation_year": 2026, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 8, "roles": ["Incoming SWE Intern", "Al/ML INTERN", "SOFTWARE DEVELOPER INTERN, PRO-SPACE", "IIT BOMBAY CONTINGENT, INTER-IIT TECH MEET 13.0"], "durations": ["Summer", "May 2024 - Jul. 2024", "Feb. 2024 - May 2024", "Nov. 2024 - Dec. 2024"], "companies": ["Google India Pvt. Ltd.", "Flomoney Pvt. Ltd.", "A&amp;PL", "Dream-11 Predictive Al Team Builder IT yy"], "locations": ["onsite", "remote", "onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Pushkar Chandrakant Narkhede", "email": "pushkarnarkhede@gmail.com", "phone": "+91 8983122461", "college": "SSBT College of Engineering, Jalgaon, Maharashtra", "skills": ["Collaborator", "Communicator", "Innovator", "Planner", "Thinker", "User Experience Design", "Agile Development Methodologies", "Cross-Functional Team Collaboration", "Software Development Life Cycle", "Technical Documentation", "Requirement Gathering", "Stakeholder Engagement", "Performance Optimization", "Responsive Web Design"], "graduation_year": 2021, "certification": [], "experience": 1, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Pushkar_Frontend_Resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Nikhlesh Shukla", "email": "nikhleshshukla123@gmail.com", "phone": "+91 7879359264", "college": "SISTec - GN Bhopal", "skills": ["Figma", "Canva", "Django", "My SQL", "SQLite", "HTML", "CSS", "Javascript", "React", "Django REST Framework", "Git", "GitHub", "Bootstrap", "Tailwind CSS", "JWT Authentication", "Al| ML", "DL Enthusiasts"], "graduation_year": 2025, "certification": ["TCS CodeVita Season 11 &amp; 12", "Smart India Hackathon (SIH) 2023 &amp; 2024"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Nikhlesh Shukla (1).pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Vinay Shrivastava", "email": "vinayshrivastava613@gmail.com", "phone": "+91-7470431954", "college": "Sagar Group of Institutions - SISTec", "skills": ["HTML", "CSS", "JAVASCRIPT", "REACT.JS", "PYTHON(Basic)", "MACHINE LEARNING"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 0, "roles": ["Front end developer", "Backend developer"], "durations": ["2 months", "3 months"], "companies": ["Real estate price prediction website", "App based solution to detect disease in lants and crops"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Main Resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Kunal Kumar", "email": "kunalroy199915@gmail.com", "phone": "+91-8709198459", "college": "Arya College of Engineering &amp; IT, Jaipur", "skills": ["Python", "Web Development", "Machine Learning", "Django", "flask", "FAST Api", "Rest Api", "Deep Learning", "MySQL", "ORM", "Kafka", "Spark", "Redis", "TensorFlow", "Pytorch", "YOLO", "NumPy", "Pandas", "Skit learn", "Lang chain", "Beautiful Sofy", "Git", "GitHub", "Gitlab", "AWS", "LLM", "MariaDB", "JavaScript", "Node.js", "React", "PostgreSQL"], "graduation_year": 2022, "certification": [], "experience": 1, "Intern_Experience": {"duration_months": 10, "roles": ["Associate Consultant", "Innovation Engineer"], "durations": ["05/2024 - present", "06/2023 - 04/2024"], "companies": ["Netzwala Services Pvt Ltd, Patna", "Stemrobo Technologies, Noida"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Kunal_CV_Python__.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "KHUSHBU NIRMAL", "email": "khushboonirmal99@gmail.com", "phone": "+91 8511377799", "college": "Gujarat Technological University", "skills": ["Python", "Django", "PyQt", "Django Rest Framework", "Docker", "Continuous Integration /Continuous Deployment (CI/CD)", "Git", "Javascript", "Pandas", "Bootstrap", "selenium", "BeautifulSoup", "WebAutomation", "CSS"], "graduation_year": 2020, "certification": ["Git Complete: The definitive, step-by-step guide to Git Certification", "Gitlab Cl - AComplete Hands-On for CI/CD Pipelines &amp; DevOps Certification", "Ultimate AWS Certified Cloud Practitioner CLF-C02 Certification"], "experience": 4, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Khushbu_Nirmal_Resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "KARTIKAY SHARMA", "email": "krtk3005@gmail.com", "phone": "7389775887", "college": "APJ Tech. University", "skills": ["Python", "SQL", "HTML", "CSS", "Cc", "Critical thinking"], "graduation_year": 2026, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 4, "roles": ["Data Analysis Intern", "Tester"], "durations": ["June 2024 - August 2024", "December 2024"], "companies": ["IBM", "Nothing India"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Kartikay Sharma_CV Resume_Internship.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Harsh Walia", "email": "harshwalia449@gmail.com", "phone": "8077014424", "college": "Gurukula Kangri Deemed to be University", "skills": ["TypeScipt", "Java", "SQL", "JavaScript", "Redis", "Postgres", "React.js", "Node.js", "Next.js", "Express", "Tailwind", "GraphQL"], "graduation_year": 2024, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 10, "roles": ["Software Developer Intern", "Full-Stack Developer Intern"], "durations": ["May 2024 \u2014 Nov 2024", "June 2023 \u2014 July 2023"], "companies": ["Autope Solutions", "Next Solutions"], "locations": ["Jaipur", "Haridwar"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Harsh_s_Resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Govinda Gupta", "email": "ag6420564@gmail.com", "phone": "+919399600645", "college": "Medi-Caps University", "skills": ["Excellent Communication", "Problem Solving", "Object Oriented Programming", "Data Structures and Algorithm", "C/C++", "Java", "Python", "HTML", "CSS", "JavaScript", "MySQL", "Machine Learning"], "graduation_year": 2024, "certification": ["JavaScript for Beginners", "Blue Prism Foundation Trainning", "Blue Prism Associate Developer", "Crash Course on Python", "Data Structures", "C/C++ for Competitive Programming"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Java Full Stack web development", "RPA (Robotics Process Automation) Blue Prism Associate Dveloper"], "durations": ["2 months", "1 month"], "companies": ["Main Flow Services and Technologies Pvt. Ltd.", "SS&amp;C"], "locations": ["Indore", "Indore"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Govinda Gupta Resume .pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Ankit Singh Sikarwar", "email": "ankitsinghsikarwar744@gmail.com", "phone": "+916263664053", "college": "Madhav Institute Of Technology and Science", "skills": ["C/C++", "Python", "JavaScript", "SQL", "HTML", "CSS/Bootstrap", "Django", "AWS", "React.js", "MS Office", "Git/Github", "Agile", "Jira", "RDBMS", "Rest API", "Linux", "FastAPI"], "graduation_year": 2023, "certification": ["Python Programming", "Basics AWS", "Basics of Html, CSS and Javascript", "Sql", "NCC \u2019C\u2019 Certificate Holder"], "experience": 1, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Ankit_sikarwarR.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Aman Maurya", "email": "amanmourya295@gmail.com", "phone": "+91 7651867685", "college": "Institute of Engineering and Rural Technology Prayagraj, India", "skills": ["HTML", "CSS", "Tailwind CSS", "Bootstrap", "Shadcn", "JavaScript", "TypeScript", "React", "Next.js", "Node.js", "Django", "Gorilla Mux", "Express", "RESTful APIs", "MongoDB", "PostgreSQL", "SQL", "NoSQL", "Mongoose ODM", "Git", "GitHub", "Python", "C", "C++", "Golang"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 16, "roles": ["Junior Developer", "MERN Stack Developer Intern"], "durations": ["Oct 2024 - Dec 2024", "Feb 2024 - Jun 2024"], "companies": ["Seetaara | Quick Commerce Platform", "Pixel Stitch | Fashion Design Al SaaS"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_100329\\Resumes_15\\Aman_SDE_Fresher-2.pdf"}</t>
+    <t>{"name": "Tanisha Kumari", "email": "tanishak2266@gmail.com", "phone": "+91 9608954838", "college": "Indian Institute of Technology (IIT) Bombay", "skills": ["Data Science", "Numpy", "Matplotlib", "MATLAB", "PyTorch", "Pandas", "NLTK", "SQL", "PostgreSQL", "PowerBI", "TensorFlow", "OpenCV"], "graduation_year": 2025, "certification": ["Machine Learning: Unsupervised Learning Recommenders and Reinforcement Learning", "Supervised Machine Learning: Regression and Classifications", "Advanced learning algorithm", "Excel: Excel Skills for Business: Essentials", "Excel: Excel Skills for Business: Intermediate I", "Excel: Excel Skills for Business: Intermediate II", "Excel: Excel Skills for Business: Advanced"], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["Operations Intern", "Data Analyst Intern"], "durations": ["Jan\u201925 - ongoing", "Jun\u201924 - Jul\u201924"], "companies": ["Freedom with AI", "NoQs Digital"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Tanisha_ Kumari.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Shivam Mane", "email": "shivam.27mane@gmail.com", "phone": "+91 9175791024", "college": "Sanjay Ghodawat Institute Kolhapur", "skills": ["Angular", "AWS", "JavaScript", "TypeScript", "PHP", "Bootstrap", "CodeIgniter", "HTML &amp; CSS"], "graduation_year": 2020, "certification": [], "experience": 3, "Intern_Experience": {"duration_months": 3, "roles": ["Frontend Web Developer - Intern"], "durations": ["2 months", "3 months"], "companies": ["SRV Media Pvt. Ltd"], "locations": ["onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Shivam-Mane-Resume-March-2025.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Rupali Chavare", "email": "rupalichavare6@gmail.com", "phone": "9834244346", "college": "Bharati Vidyapeeth University", "skills": ["Java", "Web development", "ReactJS", "Spring Boot", "Hibernate", "SQL", "JavaScript", "Angular"], "graduation_year": 2025, "certification": ["SEED Certified"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Software Development Intern"], "durations": ["6 months"], "companies": ["Codeseed"], "locations": ["Pandharpur, India"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\RupaliChavare_Cv.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "AJAY KUSHWAHA", "email": "ajayindial925@gmail.com", "phone": "+91 8932012815", "college": "KIET Group of Institutions (Affiliated to AKTU University)", "skills": ["Java", "Python", "SQL", "HTML", "CSS", "JavaScript", "RestAPI", "SpringBoot", "Django", "VS Code", "Eclipse", "GitHub", "Postman", "Data Structures and Algorithms", "Object-Oriented Programming", "Operating Systems", "Database Management Systems", "MySQL"], "graduation_year": 2024, "certification": ["Java by Coding Ninjas", "Python Programming and Machine Learning", "API Developer (Python/Django Rest/Flask/PostgreSQL/Postman)"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Frontend Developer Intern", "Java Developer Intern"], "durations": ["3 months", "4 months"], "companies": ["IBM SkillsBuild", "Wipro Limited"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\resume_AjayKushwaha.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Omkar Shirpure", "email": "22b0910@iitb.ac.in", "phone": "null", "college": "Indian Institute of Technology Bombay", "skills": ["C/C++", "Python", "Go", "Scala", "Haskell", "Lisp", "Bash", "x86 and MIPS Assembly", "VHDL", "DART", "Verilog", "React", "Next.js", "Flutter", "Node.js", "Django", "MongoDB", "PostgreSQL", "Angular", "Excel", "NumPy", "Pandas", "MatPlotLib", "SciPy", "PyTorch", "TensorFlow", "scikit-learn", "Kubernetes", "Docker", "Redis", "ELK Stack", "HiveDB", "MATLAB", "Git", "Sed", "Awk", "GDB"], "graduation_year": 2026, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 8, "roles": ["Incoming SWE Intern", "Al/ML INTERN", "SOFTWARE DEVELOPER INTERN, PRO-SPACE", "Dream-11 Predictive Al Team Builder IT yy"], "durations": ["Summer", "May 2024 - Jul. 2024", "Feb. 2024 - May 2024", "Nov. 2024 - Dec. 2024"], "companies": ["Google India Pvt. Ltd.", "Flomoney Pvt. Ltd.", "A&amp;PL", "IIT BOMBAY CONTINGENT"], "locations": ["onsite", "remote", "onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Pushkar Chandrakant Narkhede", "email": "pushkarnarkhede@gmail.com", "phone": "+91 8983122461", "college": "SSBT College of Engineering, Jalgaon, Maharashtra", "skills": ["Collaborator", "Communicator", "Innovator", "Planner", "Thinker", "User Experience Design", "Agile Development Methodologies", "Cross-Functional Team Collaboration", "Software Development Life Cycle", "Technical Documentation", "Requirement Gathering", "Stakeholder Engagement", "Performance Optimization", "Responsive Web Design"], "graduation_year": 2021, "certification": [], "experience": 1, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Pushkar_Frontend_Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Nikhlesh Shukla", "email": "nikhleshshukla123@gmail.com", "phone": "+91 7879359264", "college": "SISTec - GN Bhopal", "skills": ["Figma", "Canva", "Django", "My SQL", "SQLite", "HTML", "CSS", "Javascript", "React", "Django REST Framework", "Git", "GitHub", "Bootstrap", "Tailwind CSS", "JWT Authentication", "Al| ML", "DL Enthusiasts"], "graduation_year": 2025, "certification": ["TCS CodeVita Season 11 &amp; 12", "Smart India Hackathon (SIH) 2023 &amp; 2024"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Nikhlesh Shukla (1).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Vinay Shrivastava", "email": "vinayshrivastava613@gmail.com", "phone": "+91-7470431954", "college": "Sagar Group of Institutions - SISTec", "skills": ["HTML", "CSS", "JAVASCRIPT", "REACT.JS", "PYTHON(Basic)", "MACHINE LEARNING"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 0, "roles": ["Front end developer", "Backend developer"], "durations": ["2 months", "3 months"], "companies": ["Real estate price prediction website", "App based solution to detect disease in lants and crops"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Main Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Kunal Kumar", "email": "kunalroy199915@gmail.com", "phone": "+91-8709198459", "college": "Arya College of Engineering &amp; IT, Jaipur", "skills": ["Python", "Web Development", "Machine Learning", "Django", "flask", "FAST Api", "Rest Api", "Deep Learning", "MySQL", "ORM", "Kafka", "Spark", "Redis", "TensorFlow", "Pytorch", "YOLO", "NumPy", "Pandas", "Skit learn", "Lang chain", "Beautiful Sofy", "Git", "GitHub", "Gitlab", "AWS", "LLM", "MariaDB", "JavaScript", "Node.js", "React", "PostgreSQL"], "graduation_year": 2022, "certification": [], "experience": 1, "Intern_Experience": {"duration_months": 10, "roles": ["Associate Consultant", "Innovation Engineer"], "durations": ["05/2024 - present", "06/2023 - 04/2024"], "companies": ["Netzwala Services Pvt Ltd, Patna", "Stemrobo Technologies, Noida"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Kunal_CV_Python__.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "KHUSHBU NIRMAL", "email": "khushboonirmal99@gmail.com", "phone": "+91 8511377799", "college": "Gujarat Technological University", "skills": ["Python", "Django", "PyQt", "Django Rest Framework", "Docker", "Continuous Integration /Continuous Deployment (CI/CD)", "Git", "Javascript", "Pandas", "Bootstrap", "selenium", "BeautifulSoup", "WebAutomation", "CSS"], "graduation_year": 2020, "certification": ["Git Complete: The definitive, step-by-step guide to Git Certification", "Gitlab Cl - AComplete Hands-On for CI/CD Pipelines &amp; DevOps Certification", "Ultimate AWS Certified Cloud Practitioner CLF-C02 Certification"], "experience": 4, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Khushbu_Nirmal_Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "KARTIKAY SHARMA", "email": "krtk3005@gmail.com", "phone": "7389775887", "college": "APJ Tech. University", "skills": ["Python", "SQL", "HTML", "CSS", "Cc", "Critical thinking"], "graduation_year": 2026, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 4, "roles": ["Data Analysis Intern", "Tester"], "durations": ["June 2024 - August 2024", "December 2024"], "companies": ["IBM", "Nothing India"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Kartikay Sharma_CV Resume_Internship.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Harsh Walia", "email": "harshwalia449@gmail.com", "phone": "8077014424", "college": "Gurukula Kangri Deemed to be University", "skills": ["TypeScipt", "Java", "SQL", "JavaScript", "Redis", "Postgres", "React.js", "Node.js", "Next.js", "Express", "Tailwind", "GraphQL"], "graduation_year": 2024, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 10, "roles": ["Software Developer Intern", "Full-Stack Developer Intern"], "durations": ["May 2024 \u2014 Nov 2024", "June 2023 \u2014 July 2023"], "companies": ["Autope Solutions", "Next Solutions"], "locations": ["Jaipur", "Haridwar"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Harsh_s_Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Govinda Gupta", "email": "ag6420564@gmail.com", "phone": "+919399600645", "college": "Medi-Caps University", "skills": ["Excellent Communication", "Problem Solving", "Object Oriented Programming", "Data Structures and Algorithm", "C/C++", "Java", "Python", "HTML", "CSS", "JavaScript", "MySQL", "Machine Learning"], "graduation_year": 2024, "certification": ["JavaScript for Beginners", "Blue Prism Foundation Trainning", "Blue Prism Associate Developer", "Crash Course on Python", "Data Structures", "C/C++ for Competitive Programming"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Java Full Stack web development", "RPA (Robotics Process Automation) Blue Prism Associate Dveloper"], "durations": ["2 months", "1 month"], "companies": ["Main Flow Services and Technologies Pvt. Ltd.", "SS&amp;C"], "locations": ["Indore", "Indore"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Govinda Gupta Resume .pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Ankit Singh Sikarwar", "email": "ankitsinghsikarwar744@gmail.com", "phone": "+916263664053", "college": "Madhav Institute Of Technology and Science", "skills": ["C/C++", "Python", "JavaScript", "SQL", "HTML", "CSS/Bootstrap", "Django", "AWS", "React.js", "MS Office", "Git/Github", "Agile", "Jira", "RDBMS", "Rest API", "Linux", "FastAPI"], "graduation_year": 2023, "certification": ["Python Programming", "Basics AWS", "Basics of Html, CSS and Javascript", "Sql", "NCC \u2019C\u2019 Certificate Holder"], "experience": 1, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Ankit_sikarwarR.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Aman Maurya", "email": "amanmourya295@gmail.com", "phone": "+91 7651867685", "college": "Institute of Engineering and Rural Technology Prayagraj, India", "skills": ["HTML", "CSS", "Tailwind CSS", "Bootstrap", "Shadcn", "JavaScript", "TypeScript", "React", "Next.js", "Node.js", "Django", "Gorilla Mux", "Express", "RESTful APIs", "MongoDB", "PostgreSQL", "SQL", "NoSQL", "Mongoose ODM", "Git", "GitHub", "Python", "C", "C++", "Golang"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 16, "roles": ["Junior Developer", "MERN Stack Developer Intern"], "durations": ["Oct 2024 - Dec 2024", "Feb 2024 - Jun 2024"], "companies": ["Seetaara | Quick Commerce Platform", "Pixel Stitch | Fashion Design Al SaaS"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Aman_SDE_Fresher-2.pdf"}</t>
   </si>
 </sst>
 </file>
@@ -496,7 +496,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="2">
-        <v>45757.41992902311</v>
+        <v>45757.87430784741</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -507,7 +507,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2">
-        <v>45757.41987133458</v>
+        <v>45757.87419346441</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -518,7 +518,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="2">
-        <v>45757.41982598238</v>
+        <v>45757.87415073733</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -529,7 +529,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="2">
-        <v>45757.41978561435</v>
+        <v>45757.8741136278</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -540,7 +540,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="2">
-        <v>45757.41973347819</v>
+        <v>45757.87406540208</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -551,7 +551,7 @@
         <v>23</v>
       </c>
       <c r="C7" s="2">
-        <v>45757.41964460594</v>
+        <v>45757.8739795197</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -562,7 +562,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>45757.4195675094</v>
+        <v>45757.87389395763</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -573,7 +573,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="2">
-        <v>45757.41952049622</v>
+        <v>45757.87384940131</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -584,7 +584,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="2">
-        <v>45757.41947599993</v>
+        <v>45757.87380798391</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -595,7 +595,7 @@
         <v>27</v>
       </c>
       <c r="C11" s="2">
-        <v>45757.41941820084</v>
+        <v>45757.87375298145</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -606,7 +606,7 @@
         <v>28</v>
       </c>
       <c r="C12" s="2">
-        <v>45757.41937317952</v>
+        <v>45757.87370383598</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -617,7 +617,7 @@
         <v>29</v>
       </c>
       <c r="C13" s="2">
-        <v>45757.41933527299</v>
+        <v>45757.87365913988</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -628,7 +628,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="2">
-        <v>45757.41928781754</v>
+        <v>45757.87361785979</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -639,7 +639,7 @@
         <v>31</v>
       </c>
       <c r="C15" s="2">
-        <v>45757.4192108502</v>
+        <v>45757.87356046819</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -650,7 +650,7 @@
         <v>32</v>
       </c>
       <c r="C16" s="2">
-        <v>45757.41915873464</v>
+        <v>45757.87350262002</v>
       </c>
     </row>
   </sheetData>

--- a/resume_parsed.xlsx
+++ b/resume_parsed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>filename</t>
   </si>
@@ -70,58 +70,100 @@
     <t>Aman_SDE_Fresher-2.pdf</t>
   </si>
   <si>
-    <t>{"name": "Tanisha Kumari", "email": "tanishak2266@gmail.com", "phone": "+91 9608954838", "college": "Indian Institute of Technology (IIT) Bombay", "skills": ["Data Science", "Numpy", "Matplotlib", "MATLAB", "PyTorch", "Pandas", "NLTK", "SQL", "PostgreSQL", "PowerBI", "TensorFlow", "OpenCV"], "graduation_year": 2025, "certification": ["Machine Learning: Unsupervised Learning Recommenders and Reinforcement Learning", "Supervised Machine Learning: Regression and Classifications", "Advanced learning algorithm", "Excel: Excel Skills for Business: Essentials", "Excel: Excel Skills for Business: Intermediate I", "Excel: Excel Skills for Business: Intermediate II", "Excel: Excel Skills for Business: Advanced"], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["Operations Intern", "Data Analyst Intern"], "durations": ["Jan\u201925 - ongoing", "Jun\u201924 - Jul\u201924"], "companies": ["Freedom with AI", "NoQs Digital"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Tanisha_ Kumari.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Shivam Mane", "email": "shivam.27mane@gmail.com", "phone": "+91 9175791024", "college": "Sanjay Ghodawat Institute Kolhapur", "skills": ["Angular", "AWS", "JavaScript", "TypeScript", "PHP", "Bootstrap", "CodeIgniter", "HTML &amp; CSS"], "graduation_year": 2020, "certification": [], "experience": 3, "Intern_Experience": {"duration_months": 3, "roles": ["Frontend Web Developer - Intern"], "durations": ["2 months", "3 months"], "companies": ["SRV Media Pvt. Ltd"], "locations": ["onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Shivam-Mane-Resume-March-2025.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Rupali Chavare", "email": "rupalichavare6@gmail.com", "phone": "9834244346", "college": "Bharati Vidyapeeth University", "skills": ["Java", "Web development", "ReactJS", "Spring Boot", "Hibernate", "SQL", "JavaScript", "Angular"], "graduation_year": 2025, "certification": ["SEED Certified"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Software Development Intern"], "durations": ["6 months"], "companies": ["Codeseed"], "locations": ["Pandharpur, India"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\RupaliChavare_Cv.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "AJAY KUSHWAHA", "email": "ajayindial925@gmail.com", "phone": "+91 8932012815", "college": "KIET Group of Institutions (Affiliated to AKTU University)", "skills": ["Java", "Python", "SQL", "HTML", "CSS", "JavaScript", "RestAPI", "SpringBoot", "Django", "VS Code", "Eclipse", "GitHub", "Postman", "Data Structures and Algorithms", "Object-Oriented Programming", "Operating Systems", "Database Management Systems", "MySQL"], "graduation_year": 2024, "certification": ["Java by Coding Ninjas", "Python Programming and Machine Learning", "API Developer (Python/Django Rest/Flask/PostgreSQL/Postman)"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Frontend Developer Intern", "Java Developer Intern"], "durations": ["3 months", "4 months"], "companies": ["IBM SkillsBuild", "Wipro Limited"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\resume_AjayKushwaha.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Omkar Shirpure", "email": "22b0910@iitb.ac.in", "phone": "null", "college": "Indian Institute of Technology Bombay", "skills": ["C/C++", "Python", "Go", "Scala", "Haskell", "Lisp", "Bash", "x86 and MIPS Assembly", "VHDL", "DART", "Verilog", "React", "Next.js", "Flutter", "Node.js", "Django", "MongoDB", "PostgreSQL", "Angular", "Excel", "NumPy", "Pandas", "MatPlotLib", "SciPy", "PyTorch", "TensorFlow", "scikit-learn", "Kubernetes", "Docker", "Redis", "ELK Stack", "HiveDB", "MATLAB", "Git", "Sed", "Awk", "GDB"], "graduation_year": 2026, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 8, "roles": ["Incoming SWE Intern", "Al/ML INTERN", "SOFTWARE DEVELOPER INTERN, PRO-SPACE", "Dream-11 Predictive Al Team Builder IT yy"], "durations": ["Summer", "May 2024 - Jul. 2024", "Feb. 2024 - May 2024", "Nov. 2024 - Dec. 2024"], "companies": ["Google India Pvt. Ltd.", "Flomoney Pvt. Ltd.", "A&amp;PL", "IIT BOMBAY CONTINGENT"], "locations": ["onsite", "remote", "onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Pushkar Chandrakant Narkhede", "email": "pushkarnarkhede@gmail.com", "phone": "+91 8983122461", "college": "SSBT College of Engineering, Jalgaon, Maharashtra", "skills": ["Collaborator", "Communicator", "Innovator", "Planner", "Thinker", "User Experience Design", "Agile Development Methodologies", "Cross-Functional Team Collaboration", "Software Development Life Cycle", "Technical Documentation", "Requirement Gathering", "Stakeholder Engagement", "Performance Optimization", "Responsive Web Design"], "graduation_year": 2021, "certification": [], "experience": 1, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Pushkar_Frontend_Resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Nikhlesh Shukla", "email": "nikhleshshukla123@gmail.com", "phone": "+91 7879359264", "college": "SISTec - GN Bhopal", "skills": ["Figma", "Canva", "Django", "My SQL", "SQLite", "HTML", "CSS", "Javascript", "React", "Django REST Framework", "Git", "GitHub", "Bootstrap", "Tailwind CSS", "JWT Authentication", "Al| ML", "DL Enthusiasts"], "graduation_year": 2025, "certification": ["TCS CodeVita Season 11 &amp; 12", "Smart India Hackathon (SIH) 2023 &amp; 2024"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Nikhlesh Shukla (1).pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Vinay Shrivastava", "email": "vinayshrivastava613@gmail.com", "phone": "+91-7470431954", "college": "Sagar Group of Institutions - SISTec", "skills": ["HTML", "CSS", "JAVASCRIPT", "REACT.JS", "PYTHON(Basic)", "MACHINE LEARNING"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 0, "roles": ["Front end developer", "Backend developer"], "durations": ["2 months", "3 months"], "companies": ["Real estate price prediction website", "App based solution to detect disease in lants and crops"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Main Resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Kunal Kumar", "email": "kunalroy199915@gmail.com", "phone": "+91-8709198459", "college": "Arya College of Engineering &amp; IT, Jaipur", "skills": ["Python", "Web Development", "Machine Learning", "Django", "flask", "FAST Api", "Rest Api", "Deep Learning", "MySQL", "ORM", "Kafka", "Spark", "Redis", "TensorFlow", "Pytorch", "YOLO", "NumPy", "Pandas", "Skit learn", "Lang chain", "Beautiful Sofy", "Git", "GitHub", "Gitlab", "AWS", "LLM", "MariaDB", "JavaScript", "Node.js", "React", "PostgreSQL"], "graduation_year": 2022, "certification": [], "experience": 1, "Intern_Experience": {"duration_months": 10, "roles": ["Associate Consultant", "Innovation Engineer"], "durations": ["05/2024 - present", "06/2023 - 04/2024"], "companies": ["Netzwala Services Pvt Ltd, Patna", "Stemrobo Technologies, Noida"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Kunal_CV_Python__.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "KHUSHBU NIRMAL", "email": "khushboonirmal99@gmail.com", "phone": "+91 8511377799", "college": "Gujarat Technological University", "skills": ["Python", "Django", "PyQt", "Django Rest Framework", "Docker", "Continuous Integration /Continuous Deployment (CI/CD)", "Git", "Javascript", "Pandas", "Bootstrap", "selenium", "BeautifulSoup", "WebAutomation", "CSS"], "graduation_year": 2020, "certification": ["Git Complete: The definitive, step-by-step guide to Git Certification", "Gitlab Cl - AComplete Hands-On for CI/CD Pipelines &amp; DevOps Certification", "Ultimate AWS Certified Cloud Practitioner CLF-C02 Certification"], "experience": 4, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Khushbu_Nirmal_Resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "KARTIKAY SHARMA", "email": "krtk3005@gmail.com", "phone": "7389775887", "college": "APJ Tech. University", "skills": ["Python", "SQL", "HTML", "CSS", "Cc", "Critical thinking"], "graduation_year": 2026, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 4, "roles": ["Data Analysis Intern", "Tester"], "durations": ["June 2024 - August 2024", "December 2024"], "companies": ["IBM", "Nothing India"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Kartikay Sharma_CV Resume_Internship.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Harsh Walia", "email": "harshwalia449@gmail.com", "phone": "8077014424", "college": "Gurukula Kangri Deemed to be University", "skills": ["TypeScipt", "Java", "SQL", "JavaScript", "Redis", "Postgres", "React.js", "Node.js", "Next.js", "Express", "Tailwind", "GraphQL"], "graduation_year": 2024, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 10, "roles": ["Software Developer Intern", "Full-Stack Developer Intern"], "durations": ["May 2024 \u2014 Nov 2024", "June 2023 \u2014 July 2023"], "companies": ["Autope Solutions", "Next Solutions"], "locations": ["Jaipur", "Haridwar"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Harsh_s_Resume.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Govinda Gupta", "email": "ag6420564@gmail.com", "phone": "+919399600645", "college": "Medi-Caps University", "skills": ["Excellent Communication", "Problem Solving", "Object Oriented Programming", "Data Structures and Algorithm", "C/C++", "Java", "Python", "HTML", "CSS", "JavaScript", "MySQL", "Machine Learning"], "graduation_year": 2024, "certification": ["JavaScript for Beginners", "Blue Prism Foundation Trainning", "Blue Prism Associate Developer", "Crash Course on Python", "Data Structures", "C/C++ for Competitive Programming"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Java Full Stack web development", "RPA (Robotics Process Automation) Blue Prism Associate Dveloper"], "durations": ["2 months", "1 month"], "companies": ["Main Flow Services and Technologies Pvt. Ltd.", "SS&amp;C"], "locations": ["Indore", "Indore"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Govinda Gupta Resume .pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Ankit Singh Sikarwar", "email": "ankitsinghsikarwar744@gmail.com", "phone": "+916263664053", "college": "Madhav Institute Of Technology and Science", "skills": ["C/C++", "Python", "JavaScript", "SQL", "HTML", "CSS/Bootstrap", "Django", "AWS", "React.js", "MS Office", "Git/Github", "Agile", "Jira", "RDBMS", "Rest API", "Linux", "FastAPI"], "graduation_year": 2023, "certification": ["Python Programming", "Basics AWS", "Basics of Html, CSS and Javascript", "Sql", "NCC \u2019C\u2019 Certificate Holder"], "experience": 1, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Ankit_sikarwarR.pdf"}</t>
-  </si>
-  <si>
-    <t>{"name": "Aman Maurya", "email": "amanmourya295@gmail.com", "phone": "+91 7651867685", "college": "Institute of Engineering and Rural Technology Prayagraj, India", "skills": ["HTML", "CSS", "Tailwind CSS", "Bootstrap", "Shadcn", "JavaScript", "TypeScript", "React", "Next.js", "Node.js", "Django", "Gorilla Mux", "Express", "RESTful APIs", "MongoDB", "PostgreSQL", "SQL", "NoSQL", "Mongoose ODM", "Git", "GitHub", "Python", "C", "C++", "Golang"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 16, "roles": ["Junior Developer", "MERN Stack Developer Intern"], "durations": ["Oct 2024 - Dec 2024", "Feb 2024 - Jun 2024"], "companies": ["Seetaara | Quick Commerce Platform", "Pixel Stitch | Fashion Design Al SaaS"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250410_205744\\Resumes_15\\Aman_SDE_Fresher-2.pdf"}</t>
+    <t>{"name": "Tanisha Kumari", "email": "tanishak2266@gmail.com", "phone": "+91 9608954838", "college": "Indian Institute of Technology (IIT) Bombay", "skills": ["Data Science", "Numpy", "Matplotlib", "MATLAB", "PyTorch", "Pandas", "NLTK", "SQL", "PostgreSQL", "PowerBI", "TensorFlow", "OpenCV"], "graduation_year": 2025, "certification": ["Machine Learning: Unsupervised Learning Recommenders and Reinforcement Learning", "Supervised Machine Learning: Regression and Classifications", "Advanced learning algorithm", "Excel: Excel Skills for Business: Essentials", "Excel: Excel Skills for Business: Intermediate I", "Excel: Excel Skills for Business: Intermediate II", "Excel: Excel Skills for Business: Advanced"], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["Operations Intern", "Data Analyst Intern"], "durations": ["Jan\u201925 - ongoing", "Jun\u201924 - Jul\u201924"], "companies": ["Freedom with AI", "NoQs Digital"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Tanisha_ Kumari.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Shivam Mane", "email": "shivam.27mane@gmail.com", "phone": "+91 9175791024", "college": "Sanjay Ghodawat Institute Kolhapur", "skills": ["Angular", "AWS", "JavaScript", "TypeScript", "PHP", "Bootstrap", "CodeIgniter", "HTML &amp; CSS"], "graduation_year": 2020, "certification": [], "experience": 3, "Intern_Experience": {"duration_months": 3, "roles": ["Frontend Web Developer - Intern"], "durations": ["2 months", "3 months"], "companies": ["SRV Media Pvt. Ltd"], "locations": ["onsite"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Shivam-Mane-Resume-March-2025.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Rupali Chavare", "email": "rupalichavare6@gmail.com", "phone": "9834244346", "college": "Bharati Vidyapeeth University", "skills": ["Java", "Web development", "ReactJS", "Spring Boot", "Hibernate", "SQL", "JavaScript", "Angular"], "graduation_year": 2025, "certification": ["SEED Certified"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Software Development Intern"], "durations": ["6 months"], "companies": ["Codeseed"], "locations": ["Pandharpur, India"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\RupaliChavare_Cv.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "AJAY KUSHWAHA", "email": "ajayindial925@gmail.com", "phone": "+91 8932012815", "college": "KIET Group of Institutions (Affiliated to AKTU University)", "skills": ["Java", "Python", "SQL", "HTML", "CSS", "JavaScript", "RestAPI", "SpringBoot", "Django", "VS Code", "Eclipse", "GitHub", "Postman", "Data Structures and Algorithms", "Object-Oriented Programming", "Operating Systems", "Database Management Systems", "MySQL"], "graduation_year": 2024, "certification": ["Java by Coding Ninjas", "Python Programming and Machine Learning", "API Developer (Python/Django Rest/Flask/PostgreSQL/Postman)"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Frontend Developer Intern", "Java Developer Intern"], "durations": ["3 months", "4 months"], "companies": ["IBM SkillsBuild", "Wipro Limited"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\resume_AjayKushwaha.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Omkar Shirpure", "email": "22b0910@iitb.ac.in", "phone": "null", "college": "Indian Institute of Technology Bombay", "skills": ["C/C++", "Python", "Go", "Scala", "Haskell", "Lisp", "Bash", "x86 and MIPS Assembly", "VHDL", "DART", "Verilog", "React", "Next.js", "Flutter", "Node.js", "Django", "MongoDB", "PostgreSQL", "Angular", "Excel", "NumPy", "Pandas", "MatPlotLib", "SciPy", "PyTorch", "TensorFlow", "scikit-learn", "Kubernetes", "Docker", "Redis", "ELK Stack", "HiveDB", "MATLAB", "Git", "Sed", "Awk", "GDB"], "graduation_year": 2026, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 8, "roles": ["Incoming SWE Intern", "Al/ML INTERN", "SOFTWARE DEVELOPER INTERN, PRO-SPACE", "IIT BOMBAY CONTINGENT, INTER-IIT TECH MEET 13.0"], "durations": ["Summer", "May 2024 - Jul. 2024", "Feb. 2024 - May 2024", "Nov. 2024 - Dec. 2024"], "companies": ["Google India Pvt. Ltd.", "Flomoney Pvt. Ltd.", "A&amp;PL", "Dream-11 Predictive Al Team Builder IT yy"], "locations": ["onsite", "remote", "onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Pushkar Chandrakant Narkhede", "email": "pushkarnarkhede@gmail.com", "phone": "+91 8983122461", "college": "SSBT College of Engineering, Jalgaon, Maharashtra", "skills": ["Collaborator", "Communicator", "Innovator", "Planner", "Thinker", "User Experience Design", "Agile Development Methodologies", "Cross-Functional Team Collaboration", "Software Development Life Cycle", "Technical Documentation", "Requirement Gathering", "Stakeholder Engagement", "Performance Optimization", "Responsive Web Design"], "graduation_year": 2021, "certification": [], "experience": 1, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Pushkar_Frontend_Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Nikhlesh Shukla", "email": "nikhleshshukla123@gmail.com", "phone": "+91 7879359264", "college": "SISTec - GN Bhopal", "skills": ["Figma", "Canva", "Django", "My SQL", "SQLite", "HTML", "CSS", "Javascript", "React", "Django REST Framework", "Git", "GitHub", "Bootstrap", "Tailwind CSS", "JWT Authentication", "Al| ML", "DL Enthusiasts"], "graduation_year": 2025, "certification": ["TCS CodeVita Season 11 &amp; 12", "Smart India Hackathon (SIH) 2023 &amp; 2024"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Nikhlesh Shukla (1).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Vinay Shrivastava", "email": "vinayshrivastava613@gmail.com", "phone": "+91-7470431954", "college": "Sagar Group of Institutions - SISTec", "skills": ["HTML", "CSS", "JAVASCRIPT", "REACT.JS", "PYTHON(Basic)", "MACHINE LEARNING"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 0, "roles": ["Front end developer", "Backend developer"], "durations": ["2 months", "3 months"], "companies": ["Real estate price prediction website", "App based solution to detect disease in lants and crops"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Main Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Kunal Kumar", "email": "kunalroy199915@gmail.com", "phone": "+91-8709198459", "college": "Arya College of Engineering &amp; IT, Jaipur", "skills": ["Python", "Web Development", "Machine Learning", "Django", "flask", "FAST Api", "Rest Api", "Deep Learning", "MySQL", "ORM", "Kafka", "Spark", "Redis", "TensorFlow", "Pytorch", "YOLO", "NumPy", "Pandas", "Skit learn", "Lang chain", "Beautiful Sofy", "Git", "GitHub", "Gitlab", "AWS", "LLM", "MariaDB", "JavaScript", "Node.js", "React", "PostgreSQL"], "graduation_year": 2022, "certification": [], "experience": 1, "Intern_Experience": {"duration_months": 10, "roles": ["Associate Consultant", "Innovation Engineer"], "durations": ["05/2024 - present", "06/2023 - 04/2024"], "companies": ["Netzwala Services Pvt Ltd, Patna", "Stemrobo Technologies, Noida"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Kunal_CV_Python__.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "KHUSHBU NIRMAL", "email": "khushboonirmal99@gmail.com", "phone": "+91 8511377799", "college": "Gujarat Technological University", "skills": ["Python", "Django", "PyQt", "Django Rest Framework", "Docker", "Continuous Integration /Continuous Deployment (CI/CD)", "Git", "Javascript", "Pandas", "Bootstrap", "selenium", "BeautifulSoup", "WebAutomation", "CSS"], "graduation_year": 2020, "certification": ["Git Complete: The definitive, step-by-step guide to Git Certification", "Gitlab Cl - AComplete Hands-On for CI/CD Pipelines &amp; DevOps Certification", "Ultimate AWS Certified Cloud Practitioner CLF-C02 Certification"], "experience": 4, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Khushbu_Nirmal_Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "KARTIKAY SHARMA", "email": "krtk3005@gmail.com", "phone": "7389775887", "college": "APJ Tech. University", "skills": ["Python", "SQL", "HTML", "CSS", "Cc", "Critical thinking"], "graduation_year": 2026, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 4, "roles": ["Data Analysis Intern", "Tester"], "durations": ["June 2024 - August 2024", "December 2024"], "companies": ["IBM", "Nothing India"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Kartikay Sharma_CV Resume_Internship.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Harsh Walia", "email": "harshwalia449@gmail.com", "phone": "8077014424", "college": "Gurukula Kangri Deemed to be University", "skills": ["TypeScipt", "Java", "SQL", "JavaScript", "Redis", "Postgres", "React.js", "Node.js", "Next.js", "Express", "Tailwind", "GraphQL"], "graduation_year": 2024, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 10, "roles": ["Software Developer Intern", "Full-Stack Developer Intern"], "durations": ["May 2024 \u2014 Nov 2024", "June 2023 \u2014 July 2023"], "companies": ["Autope Solutions", "Next Solutions"], "locations": ["Jaipur", "Haridwar"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Harsh_s_Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Govinda Gupta", "email": "ag6420564@gmail.com", "phone": "+919399600645", "college": "Medi-Caps University", "skills": ["Excellent Communication", "Problem Solving", "Object Oriented Programming", "Data Structures and Algorithm", "C/C++", "Java", "Python", "HTML", "CSS", "JavaScript", "MySQL", "Machine Learning"], "graduation_year": 2024, "certification": ["JavaScript for Beginners", "Blue Prism Foundation Trainning", "Blue Prism Associate Developer", "Crash Course on Python", "Data Structures", "C/C++ for Competitive Programming"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Java Full Stack web development", "RPA (Robotics Process Automation) Blue Prism Associate Dveloper"], "durations": ["2 months", "1 month"], "companies": ["Main Flow Services and Technologies Pvt. Ltd.", "SS&amp;C"], "locations": ["Indore", "Indore"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Govinda Gupta Resume .pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Ankit Singh Sikarwar", "email": "ankitsinghsikarwar744@gmail.com", "phone": "+916263664053", "college": "Madhav Institute Of Technology and Science", "skills": ["C/C++", "Python", "JavaScript", "SQL", "HTML", "CSS/Bootstrap", "Django", "AWS", "React.js", "MS Office", "Git/Github", "Agile", "Jira", "RDBMS", "Rest API", "Linux", "FastAPI"], "graduation_year": 2023, "certification": ["Python Programming", "Basics AWS", "Basics of Html, CSS and Javascript", "Sql", "NCC \u2019C\u2019 Certificate Holder"], "experience": 1, "Intern_Experience": {"duration_months": 6, "roles": ["Python Developer Intern"], "durations": ["6 months"], "companies": ["Praedico Global Research Pvt. Ltd."], "locations": ["Gwalior"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Ankit_sikarwarR.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Aman Maurya", "email": "amanmourya295@gmail.com", "phone": "+91 7651867685", "college": "Institute of Engineering and Rural Technology Prayagraj, India", "skills": ["HTML", "CSS", "Tailwind CSS", "Bootstrap", "Shadcn", "JavaScript", "TypeScript", "React", "Next.js", "Node.js", "Django", "Gorilla Mux", "Express", "RESTful APIs", "MongoDB", "PostgreSQL", "SQL", "NoSQL", "Mongoose ODM", "Git", "GitHub", "Python", "C", "C++", "Golang"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 16, "roles": ["Junior Developer", "MERN Stack Developer Intern"], "durations": ["Oct 2024 - Dec 2024", "Feb 2024 - Jun 2024"], "companies": ["Seetaara | Quick Commerce Platform", "Pixel Stitch | Fashion Design Al SaaS"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Aman_SDE_Fresher-2.pdf"}</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:10:27</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:10:23</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:10:19</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:10:16</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:10:11</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:10:05</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:09:59</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:09:55</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:09:52</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:09:47</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:09:43</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:09:40</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:09:37</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:09:33</t>
+  </si>
+  <si>
+    <t>2025-04-14 19:09:29</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -174,12 +216,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,8 +536,8 @@
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2">
-        <v>45757.87430784741</v>
+      <c r="C2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -506,8 +547,8 @@
       <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2">
-        <v>45757.87419346441</v>
+      <c r="C3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -517,8 +558,8 @@
       <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2">
-        <v>45757.87415073733</v>
+      <c r="C4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -528,8 +569,8 @@
       <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2">
-        <v>45757.8741136278</v>
+      <c r="C5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -539,8 +580,8 @@
       <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="2">
-        <v>45757.87406540208</v>
+      <c r="C6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -550,8 +591,8 @@
       <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2">
-        <v>45757.8739795197</v>
+      <c r="C7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -561,8 +602,8 @@
       <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="2">
-        <v>45757.87389395763</v>
+      <c r="C8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -572,8 +613,8 @@
       <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2">
-        <v>45757.87384940131</v>
+      <c r="C9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -583,8 +624,8 @@
       <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="2">
-        <v>45757.87380798391</v>
+      <c r="C10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -594,8 +635,8 @@
       <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2">
-        <v>45757.87375298145</v>
+      <c r="C11" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -605,8 +646,8 @@
       <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="2">
-        <v>45757.87370383598</v>
+      <c r="C12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -616,8 +657,8 @@
       <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="2">
-        <v>45757.87365913988</v>
+      <c r="C13" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -627,8 +668,8 @@
       <c r="B14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="2">
-        <v>45757.87361785979</v>
+      <c r="C14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -638,8 +679,8 @@
       <c r="B15" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="2">
-        <v>45757.87356046819</v>
+      <c r="C15" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -649,8 +690,8 @@
       <c r="B16" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="2">
-        <v>45757.87350262002</v>
+      <c r="C16" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/resume_parsed.xlsx
+++ b/resume_parsed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>filename</t>
   </si>
@@ -25,6 +25,105 @@
     <t>created_at</t>
   </si>
   <si>
+    <t>uzair-resume.pdf</t>
+  </si>
+  <si>
+    <t>Surya_Jadhav_CV_.pdf</t>
+  </si>
+  <si>
+    <t>sreeram_updated_resume (1) (1).pdf</t>
+  </si>
+  <si>
+    <t>ShubhanshAgrawalResume.pdf</t>
+  </si>
+  <si>
+    <t>Seema_Shinde_resume (1).pdf</t>
+  </si>
+  <si>
+    <t>SDE_Resume.pdf</t>
+  </si>
+  <si>
+    <t>SDE _Normal Format.docx</t>
+  </si>
+  <si>
+    <t>SatyamYadav-1 (1) (1).pdf</t>
+  </si>
+  <si>
+    <t>SarveshMamidwarResume.pdf</t>
+  </si>
+  <si>
+    <t>Sachin_Dolase_8010417200_updated_CV.pdf</t>
+  </si>
+  <si>
+    <t>Resume_VaibhavJain (5).pdf</t>
+  </si>
+  <si>
+    <t>Resume_Sidharth.pdf</t>
+  </si>
+  <si>
+    <t>Resume_Rohit_Kumar-1.pdf</t>
+  </si>
+  <si>
+    <t>RESUME_Kavita.pdf</t>
+  </si>
+  <si>
+    <t>priyanka (Autosaved).pdf</t>
+  </si>
+  <si>
+    <t>Prabhakar_Aher_Cyncly_CV.pdf</t>
+  </si>
+  <si>
+    <t>newswiotresume2024-25.pdf</t>
+  </si>
+  <si>
+    <t>Kunj_Singhal_Resume.1 (1) (1) (1).pdf</t>
+  </si>
+  <si>
+    <t>Kumar_saurav_resume.pdf</t>
+  </si>
+  <si>
+    <t>Karthik Navalli 7_compressed.pdf</t>
+  </si>
+  <si>
+    <t>cv_siddharth_mandil_Pdf.pdf</t>
+  </si>
+  <si>
+    <t>CV_2025031115204366.pdf</t>
+  </si>
+  <si>
+    <t>Bhaskar_Jha_Resume.pdf</t>
+  </si>
+  <si>
+    <t>AnshuResume2025.pdf</t>
+  </si>
+  <si>
+    <t>Ankit_sikarwarR (1).pdf</t>
+  </si>
+  <si>
+    <t>Aman_Resume-11Sep.pdf</t>
+  </si>
+  <si>
+    <t>Aman_Resume-11Sep (1).pdf</t>
+  </si>
+  <si>
+    <t>Abhishek_Goyal.pdf</t>
+  </si>
+  <si>
+    <t>Abhinav_PK_Python_Developer.pdf</t>
+  </si>
+  <si>
+    <t>Aayush_Parashar_CV.pdf</t>
+  </si>
+  <si>
+    <t>a954018387_67a4492b5b779.pdf</t>
+  </si>
+  <si>
+    <t>21135065_Jeet _Vyas_SDE2 (1).pdf</t>
+  </si>
+  <si>
+    <t>1_Page_Ext (1).pdf</t>
+  </si>
+  <si>
     <t>Tanisha_ Kumari.pdf</t>
   </si>
   <si>
@@ -70,6 +169,105 @@
     <t>Aman_SDE_Fresher-2.pdf</t>
   </si>
   <si>
+    <t>{"name": "UZAIR UL HASSAN", "email": "uzairulhassan24@gmail.com", "phone": "9701318210", "college": "Muffakham Jah College Of Engineering and Technology", "skills": ["Javascript", "ReactJS", "TailwindCSS", "NextJS", "ExpressJS", "MongoDB", "NodeJS", "AWS", "Prisma", "Rust", "Serverless"], "graduation_year": 2024, "certification": [], "experience": 1, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\uzair-resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Surya Jadhav", "email": "surya.jadhav210@gmail.com", "phone": "+91-7083188745", "college": "Siddhant College of Engineering", "skills": ["Python", "Django", "Postgress", "React Js", "Node js", "Javascript", "SQL", "HTML", "CSS"], "graduation_year": 2023, "certification": ["Python for Data Science", "Django", "Angular Js", "Java", "Git and GitHub", "SQL"], "experience": 1, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Surya_Jadhav_CV_.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "SREERAM CHANDRA SEKHAR", "email": "sriramsriram3009@gmail.com", "phone": "+91 9390362372", "college": "National Institute Of Technology, Srinagar", "skills": ["C", "C++", "Java", "Python", "HTML", "CSS", "Database Management (SQL, Oracle)", "Multithreading", "Wireshark", "Machine Learning", "Git", "GitHub", "Basic Selenium"], "graduation_year": 2024, "certification": [], "experience": 1, "Intern_Experience": {"duration_months": 7, "roles": ["Tutor", "Web Developer Trainee"], "durations": ["6 months", "1 month"], "companies": ["Programmers Trend", "Internshala"], "locations": ["Srinagar, India", "Srinagar, India"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\sreeram_updated_resume (1) (1).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "SHUBHANSH AGRAWAL", "email": "shubhanshagrawal0311@gmail.com", "phone": "9098710276", "college": "Oriental Institute of Science and Technology", "skills": ["CORE JAVA", "MySql", "HTML", "CSS", "JavaScript", "React.js", "Express.js", "RESTful API design", "VS Code", "Github"], "graduation_year": 2024, "certification": ["Introduction to Web development HTML ,CSS , JavaScript (IBM)", "Introduction to Frontend developement (Coursera)", "Introduction to Backend Development (Coursera)"], "experience": 0, "Intern_Experience": {"duration_months": 8, "roles": ["SDE Intern"], "durations": ["8 months"], "companies": ["Primathon Technology Ventures"], "locations": ["onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\ShubhanshAgrawalResume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Seema Shinde", "email": "seemashinde230282@gmail.com", "phone": "+919075031422", "college": "D Y Patil College of Engineering &amp; Technology, Kolhapur", "skills": ["Java", "Python", "JavaScript", "C", "Django", "Angular", "Tableau", "Power BI", "MS Word", "MS Excel", "PowerPoint", "HTML", "CSS", "AWS Academy Data Analytics", "AWS Academy Cloud Foundations", "Python", "Intro into SQL", "Hindi", "Marathi"], "graduation_year": 2024, "certification": ["Machine Learning ML by NPTLE", "AWS Academy Data Analytics", "AWS Academy Cloud Foundations"], "experience": 0, "Intern_Experience": {"duration_months": 4, "roles": ["Software Trainee on Data Science and AIML", "Presentation Software Trainee"], "durations": ["2 months", "1 month"], "companies": ["Earth Logicware Technologies, Kolhapur", "AICTE Data Analytics Virtual Intership supported by AWS Academy"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Seema_Shinde_resume (1).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Subham Sharma", "email": "Shubhamsh002@gmail.com", "phone": "9875000041", "college": "Indian Institute of Technology Bombay", "skills": ["Node.js", "MongoDB", "Git", "Java", "HTML", "CSS", "SQL", "JavaScript", "React", "Express.js", "Mongoose", "Bootstrap", "Tailwind CSS"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\SDE_Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Manisha Hirasing Rathod", "email": "maniishaarathod@gmail.com", "phone": "9307744151", "college": "MKSSS\u2019s Cummins College of Engineering for Women, Pune", "skills": ["DATA STRUCTURE AND ALGORITHM", "OBJECT ORIENTED PROGRAMMING", "JAVA", "C and C++", "DATABASE MANAGEMENT SYSTEM", "MYSQL", "MACHINE LEARNING", "DEEP LEARNING", "HTML"], "graduation_year": 2025, "certification": ["Cummins Soft Skill Certificate"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\SDE _Normal Format.docx"}</t>
+  </si>
+  <si>
+    <t>{"name": "Satyam Yadav", "email": "imsatyam243@gmail.com", "phone": "+91 9569038600", "college": "Babu Banarasi Das University, Lucknow", "skills": ["JavaScript (ES6+)", "Python", "HTML", "CSS", "React.js", "Redux Toolkit", "Bootstrap", "Tailwind CSS", "Django", "REST APIs", "JSON", "MySQL", "MongoDB", "Git", "GitHub", "NPM", "VS Code", "IntelliJ", "Webex", "Functional Programming", "OOPs", "Data Structures &amp; Algorithms (DSA)", "Computer Networks", "DBMS"], "graduation_year": 2024, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 8, "roles": ["Software Engineer Intern"], "durations": ["2 months", "6 months"], "companies": ["Indsac Softech"], "locations": ["Bangalore, Karnataka"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\SatyamYadav-1 (1) (1).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Sarvesh Mamidwar", "email": "sarvesh.mamidwar21@gmail.com", "phone": "Not available", "college": "University Of Pune", "skills": ["Full Stack Java Developer", "Java", "Spring Boot", "Spring Framework", "Spring Security", "Spring MVC", "Microservices Architecture", "API Gateway", "Load Balancing", "Hibernate", "MySQL", "JDBC", "Servlets", "C", "HTML", "CSS", "Thymeleaf", "JavaScript", "OOPS", "JSP", "REST APIs", "Git", "Maven", "English", "Marathi", "Hindi"], "graduation_year": 2023, "certification": ["T Java Full Stack Developer", "U SQL and Relational Databases Provided by IBM", "J Machine Learning with OpenCV", "6th International Conference on Ideas, Innovations and Impact in Science and Technology"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\SarveshMamidwarResume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Sachin Dolase", "email": "sachindolase09@gmail.com", "phone": "+91 8010417200", "college": "Ajeenkya D Y Patil University Of Pune", "skills": ["HTML5", "MongoDB", "CSS3", "React", "Javascript", "Node.js", "Tailwind.css", "Express.js", "Bootstrap", "Git/Github", "Firebase", "Rest API\u2019s", "Next.js", "Typescript"], "graduation_year": 2024, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 9, "roles": ["Node.js Developer intern", "Junior Front end Developer"], "durations": ["7 months", "3 months"], "companies": ["Ekka", "Baoiam Innovations"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Sachin_Dolase_8010417200_updated_CV.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Vaibhav Jain", "email": "vaibhavjain7171@gmail.com", "phone": "+91-8600948208", "college": "Modern Education Society\u2019s College of Engineering (MESCOE), Pune", "skills": ["Java", "C++", "JavaScript", "SQL", "Spring Boot", "Hibernate", "J2EE", "HTML5", "CSS", "Bootstrap", "ReactJS", "NodeJS", "ExpressJs", "MongoDB", "VS Code", "IntelliJ IDEA", "STS", "Git", "Data Structures &amp; Algorithms (DSA)", "Database Management System (DBMS)", "Operating Systems", "Object-Oriented Programming (OOPS)"], "graduation_year": 2023, "certification": ["Alpha batch(DSA course) - Apna college", "Google cloud bootcamp - GFG", "Java Full Stack LIVE Course - Spark 2.0"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Resume_VaibhavJain (5).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Sidharth Mahajan", "email": "sidharthmahajan74@gmail.com", "phone": "+917828068116", "college": "Thakur Shivkumar Singh Memorial Engineering College, Jhiri", "skills": ["Front End Developer", "Full Stack Web Development", "Debugging", "Empowering aspiring coders", "Coding Ninjas", "TA-Full Stack Web Development", "Java", "HTML5", "CSS3", "JavaScript", "React.js", "MongoDb", "VS Code", "GitHub", "Bootstrap", "DSA", "Communication", "Teamwork"], "graduation_year": 2023, "certification": ["Introduction to JAVA - Coding Ninjas", "Data Structures in JAVA - Coding Ninjas", "Front End | Full Stack Web Development - Coding Ninjas", "Back End | Full Stack Web Development - Coding Ninjas", "Myntra Clone - E-commerce Website - Coding Ninjas", "React | Full Stack Development - Coding Ninjas", "Todo App - Task Management Tool - Coding Ninjas", "Amazon Front Page Clone - Ecommerce UI - Coding Ninjas"], "experience": 0, "Intern_Experience": {"duration_months": 4, "roles": ["TA-Full Stack Web Development"], "durations": ["3 months", "1 month"], "companies": ["Coding Ninjas"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Resume_Sidharth.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "ROHIT KUMAR", "email": "anujrohitkumar3010@gmail.com", "phone": "+91-9580229633", "college": "KIET Group of Institutions, Ghaziabad", "skills": ["Java", "JavaScript", "Python", "React", "Node.js", "Spring Boot", "RESTful APIs", "MongoDB", "MySQL", "PostgreSQL", "VS Code", "NetBeans IDE", "IntelliJ", "Git", "GitHub", "Cybersecurity Basics", "Version Control"], "graduation_year": 2024, "certification": ["Data Structures (Coursera) \u2013 University of California, San Diego (06/2023)", "Algorithmic Toolbox (Coursera) \u2013 University of California, San Diego (2021)", "Java Programming (Coursera) \u2013 Duke University (2021)"], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["Completed Modules on Cloud Security, Introduction to Cybersecurity, Introduction to Packet Tracer, Cybersecurity essentials", "Conducted Study on the imaginary Network, evaluated its vulnerability and Developed solution Network overcoming its weakness", "Implemented a Network in Cisco Packet Tracer. Composed a PPT explaining the modules used in that network in depth", "Learned About Java Programming and OOPS Concepts. Completed MOOC Course on Great Learning Namely OOPS By Great Learning", "Build a GUI Based Application, Namely Temperature Converter. This was Created on NetBeans IDE 15 Harnessing Learnings of Internship"], "durations": ["Oct\u20192024 \u2013 Dec\u20192024", "Cisco Virtual Internship", "CPI-D Internship"], "companies": ["Texity Technology Pvt. Ltd", "Cisco", "CPI-D"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Resume_Rohit_Kumar-1.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Kavita Prajapati", "email": "prajpatikavita132004@gmail.com", "phone": "+91 9685252642", "college": "Sagar Institute Of Research And Technology-Exellence", "skills": ["C", "C++", "JavaSE", "Python", "HTML", "CSS", "JavaScript", "SQL", "Git", "REST APIs", "Spring Boot", "Spring Core", "Spring MVC", "Django", "Bootstrap", "ReactJS", "MongoDB", "MySQL Workbench"], "graduation_year": 2025, "certification": ["Walmart USA - Advanced Software Engineering"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\RESUME_Kavita.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Priyanka Yadav", "email": "priyankayadavyy01@gmail.com", "phone": "+91-9369330560", "college": "Institute of Engineering &amp; Rural Technology, Prayagraj", "skills": ["React", "JavaScript", "Tailwind", "HTML5", "CSS3", "React props and hooks", "Framer-motion", "CorelDraw", "Express &amp; Node JS", "Python", "MongoDB", "Cloudinary", "Bootstrap", "Git &amp; Github", "REST API", "React + Vite", "Coffero", "Google Data Analytics", "Google UX Design", "AI Tools", "Python"], "graduation_year": 2024, "certification": ["Google Data Analytics", "Google UX Design", "AI Tools", "Python"], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["Frontend Developer", "Web Developer"], "durations": ["8 weeks", "8 months"], "companies": ["Reliale Edutech", "Aashman Foundation"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\priyanka (Autosaved).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Prabhakar Aher", "email": "prabhakaraher13@gmail.com", "phone": "9552602705", "college": "Pune University", "skills": ["JavaScript", "TypeScript", "React.js", "jQuery", "HTML5", "CSS3", "Bootstrap", "Git", "MS Azure", "Scrum", "Kanban"], "graduation_year": 2025, "certification": [], "experience": 2, "Intern_Experience": {"duration_months": 6, "roles": ["Frontend Developer Intern"], "durations": ["7 months"], "companies": ["Cyncly India Pvt Ltd"], "locations": ["onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Prabhakar_Aher_Cyncly_CV.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Deepak Pandey", "email": "deepakgpandey05@gmail.com", "phone": "+919827678994", "college": "Sagar Institute Of Research And Technology", "skills": ["Java", "SQL", "JavaScript", "HTML", "CSS", "Reactjs", "ProblemSolving", "Nodejs", "Expressjs", "Object-OrientedProgramming", "GoodCommunication", "Leadership", "TeamWork"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 0, "roles": ["Software Developer", "Hardware Integration Specialist"], "durations": ["2 months", "2 months"], "companies": ["Personal Project", "Personal Project"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\newswiotresume2024-25.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Kunjsinghal108", "email": "kunjsinghal108@gmail.com", "phone": "+91 9917354112", "college": "Galgotias University", "skills": ["Algorithm and Data Structures", "Advanced Excel", "Tableau", "RDBMS", "Java", "Front-End Web Development", "C", "C++", "Python", "HTML", "CSS", "Javascript", "React Js"], "graduation_year": 2024, "certification": ["IBM SkillsBuild", "HARSH AKSHIT LEAD, GOOGLE DEVELOPER GROUP"], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["Designer", "Front-End Development Intern"], "durations": ["2 months", "3 months"], "companies": ["DineVerse", "Blue Birds International School"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Kunj_Singhal_Resume.1 (1) (1) (1).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "KUMAR SAURAV", "email": "saurav.id.div@gmail.com", "phone": "+91-8298149971", "college": "Galgotias University", "skills": ["Leadership", "Decision Making", "Teamwork", "Patience", "JavaScript", "Java", "Node.js", "Express.js", "Tailwind CSS", "MongoDB", "Excel", "API Integration", "GitHub"], "graduation_year": 2024, "certification": ["Web Development from Scratch", "Advanced Diploma in Computer Applications", "AMCAT"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Kumar_saurav_resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Karthik Navalli", "email": "karthiknavalli24@gmail.com", "phone": "+91-8197056525", "college": "BLDEA\u2019s Dr. P. G. Halakatti College of Engineering and Technology, Vijayapura", "skills": ["Python", "HTML", "CSS", "JavaScript", "Java", "C", "C++", "PHP", "VSCode", "Eclipse IDE", "GitHub", "PyCharm", "Django", "Bootstrap", "Flask", "jQuery", "Node.js", "Express.js", "Angular.js", "React.js", "PostgreSQL", "SQL", "MySQL", "MongoDB", "Unix", "Linux", "Docker", "Kubernetes", "Jenkins", "Ansible", "Nagios", "Puppet", "Maven", "Gradle", "Tkinter", "Pandas", "Turtle", "SMTP", "Active Listening", "Leadership", "Strong Work Ethic"], "graduation_year": 2025, "certification": ["NPTEL- Joy of Computing using Python (IIT Madras)", "NPTEL- Programming in Java (IIT Kharagpur)"], "experience": 0, "Intern_Experience": {"duration_months": 2, "roles": ["Web development internship", "Python internship"], "durations": ["1 month", "1 month"], "companies": ["SystemTron", "Codesoft"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Karthik Navalli 7_compressed.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Siddharth Mandil", "email": "siddharthmandilwork@gmail.com", "phone": "8827319380", "college": "ITM Group of Institution, Gwalior", "skills": ["C", "C++", "Python", "Django", "SQL", "HTML5", "CSS", "JavaScript", "Bootstrap", "jQuery", "Power BI"], "graduation_year": 2023, "certification": ["Certification in Python Programming", "Certification in C Programming", "Certification in C++ Programming"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Python Developer (Intern)"], "durations": ["6 months"], "companies": ["Ypsilon IT Solutions Pvt Ltd"], "locations": ["onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\cv_siddharth_mandil_Pdf.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Om Shankar Mishra", "email": "osmjsr@gmail.com", "phone": "9693947417", "college": "Ardent Computech Pvt Ltd.", "skills": ["JavaScript", "HTML5", "CSS3", "React", "Node.js", "Express", "MongoDB", "Git", "npm", "yarn", "Windows", "Java", "Python", "SQL", "WordPress", "PHP", "C", "Excel", "Advance Excel"], "graduation_year": 2025, "certification": [], "experience": 1, "Intern_Experience": {"duration_months": 6, "roles": ["Full Stack Web Development using MERN Internship Trainee"], "durations": ["3 months"], "companies": ["Ardent Computech Pvt Ltd."], "locations": ["onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\CV_2025031115204366.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Bhaskar Jha", "email": "jhabhaskar950@gmail.com", "phone": null, "college": "Haldia Institute Of Technology", "skills": ["Java", "JavaScript", "Python", "C", "SQL", "React.js", "Redux Toolkit", "Tailwind CSS", "AWS(EC2, S3, Lambda)", "CSS 3", "HTML", "Git &amp; GitHub", "Linux"], "graduation_year": 2026, "certification": ["Java Programming: Solving Problems with Software | Coursera"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Bhaskar_Jha_Resume.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Anshu Kumar Singh", "email": "anshusingh9907@gmail.com", "phone": "+91-8305177663", "college": "Shri Vaishnav Vidyapeeth Vishwavidyalaya, Indore", "skills": ["Python", "SQL", "JavaScript", "Django", "FastAPI", "MySQL", "SQLite", "Git", "Postman", "REST API Development", "Backend Development", "Linux"], "graduation_year": 2025, "certification": ["Python Foundation Certification (Infosys)", "Google Data Analytics Certification"], "experience": 0, "Intern_Experience": {"duration_months": 2, "roles": ["Infosys Springboard Project Intern"], "durations": ["2 months"], "companies": ["Infosys"], "locations": ["onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\AnshuResume2025.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Ankit Singh Sikarwar", "email": "ankitsinghsikarwar744@gmail.com", "phone": "+916263664053", "college": "Madhav Institute Of Technology and Science, Gwalior", "skills": ["C/C++", "Python", "JavaScript", "SQL", "HTML", "CSS/Bootstrap", "Django", "AWS", "React.js", "MSOffice", "Git/Github", "Agile", "Jira", "RDBMS", "RestAPI", "Linux", "FastAPI"], "graduation_year": 2023, "certification": ["Python Programming - Udemy", "Basics AWS on Udemy", "Basic of Html, Css and Javascript on Udemy", "Sql on Udemy", "NCC' C' Certificate Holder"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Ankit_sikarwarR (1).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Aman Mishra", "email": "amanmishra.am.658@gmail.com", "phone": "+91 8966823389", "college": "Oriental College of Technology", "skills": ["Python", "SQL", "PySpark", "Azure Data Factory", "Azure Databricks", "ETL processes", "Data Warehousing", "Data Modeling", "Microsoft Azure", "Apache Spark", "SparkSQL", "Azure Synapse Analytics", "Azure Data Storage", "Azure Data Factory", "Git", "GitHub", "Microsoft Excel", "Windows", "Linux(Ubuntu)"], "graduation_year": 2022, "certification": ["Microsoft-Azure Fundamentals(AZ-900)", "Microsoft-Azure Data Fundamentals(DP-900)"], "experience": 2, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Aman_Resume-11Sep.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Aman Mishra", "email": "amanmishra.am.658@gmail.com", "phone": "+91 8966823389", "college": "Oriental College of Technology", "skills": ["Python", "SQL", "PySpark", "Azure Data Factory", "Azure Databricks", "ETL processes", "Data Warehousing", "Data Modeling", "Microsoft Azure", "Apache Spark", "SparkSQL", "Azure Synapse Analytics", "Azure Data Storage", "Azure Data Factory", "Git", "GitHub", "Microsoft Excel", "Windows", "Linux(Ubuntu)"], "graduation_year": 2022, "certification": ["Microsoft-Azure Fundamentals(AZ-900)", "Microsoft-Azure Data Fundamentals(DP-900)"], "experience": 2, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Aman_Resume-11Sep (1).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Abhishek Goyal", "email": "abhigoyal0510@gmail.com", "phone": "+91 9045647246", "college": "Poornima University, Jaipur DBRAU, Agra, Uttar Pradesh", "skills": ["Flutter Development", "Google Cloud/Firebase", "Object-Oriented Programming (OOP)", "Git", "Bitbucket", "Jira", "Android Studio", "PyCharm", "Python Development &amp; Scripting", "Data science modelling and analysis using libraries such as NumPy, Pandas, Matplotlib"], "graduation_year": 2024, "certification": [], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Abhishek_Goyal.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Abhinav P K", "email": "abhinav.pk@hotmail.com", "phone": "+917034654496", "college": "MAHATMA GANDHI COLLEGE", "skills": ["Python", "Django", "Django REST Framework", "C", "C++", "HTML", "CSS", "JavaScript", "SQL", "Django REST Framework", "Celery", "RabbitMQ", "MySQL", "PostgreSQL", "Git", "GitHub", "VSCode", "Jupyter Notebook", "Postman"], "graduation_year": 2021, "certification": ["Python Programming Certified User"], "experience": 0, "Intern_Experience": {"duration_months": 6, "roles": ["Python/Django Developer Intern", "Backend Developer Intern"], "durations": ["2 months", "3 months"], "companies": ["KARMAALAB", "IMIOTTECHNOLABS"], "locations": ["Bangalore, Karnataka", "Kannur, Kerala"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Abhinav_PK_Python_Developer.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Aayush Parashar", "email": "ayushparashar6203@gmail.com", "phone": "+91-8102441352", "college": "Oriental College of Technology Bhopal, India", "skills": ["JavaScript", "NodeJS", "ExpressJS", "REST API", "GIT", "PostgreSQL", "MongoDB", "Leadership", "Product Management", "Public Speaking", "Time Management"], "graduation_year": 2024, "certification": ["Certificate of Excellence in Java by Coding Ninjas", "Certificate of Completion Data Structure and Algorithms by Coding Ninjas", "Problem Solving(Basic) by Hacker Rank", "Java(Basic) Certificate by Hacker Rank"], "experience": 1, "Intern_Experience": {"duration_months": 4, "roles": ["Product Management Fellow"], "durations": ["2 months", "2 months"], "companies": ["NextLeap Remote"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\Aayush_Parashar_CV.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Akash Sharma", "email": "officialmailakashsharma@gmail.com", "phone": "+91 9540183487", "college": "Institute of Engineering and Rural Technology Allahabad, UP", "skills": ["HTML", "CSS", "Tailwind CSS", "Bootstrap", "Shadcn", "JavaScript", "TypeScript", "React", "Next.js", "Node.js", "Django", "Express", "RESTful APIs", "MongoDB", "SQL", "NoSQL", "Mongoose ODM", "Git", "GitHub", "Python", "C", "C++", "JavaScript", "TypeScript"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["Built a cloud-based Integrated Development Environment (IDE) supporting multiple programming languages.", "Implemented real-time code collaboration using WebSockets for enhanced developer teamwork.", "Utilized Docker and Kubernetes to create isolated development environments for scalability and deployment.", "Developed backend services with Node.js and REST APIs to handle file management, compilation, and execution of code.", "Designed an intuitive user interface with ReactJS for seamless coding and project management.", "Developed an interactive media player platform using React for the front end and Node.js for the backend.", "Implemented functionalities like media upload, playlist management, and playback features.", "Created a responsive and engaging user interface using MaterialUI for better user experience.", "Utilized MongoDB for user data storage and Express.js for API management, ensuring seamless data interaction.", "Developed a full-featured attendance management system using the MERN stack for educational institutions.", "Implemented functionalities such as marking attendance, generating attendance reports, and tracking student progress.", "Created an intuitive and easy-to-use dashboard for administrators and teachers using React and Bootstrap.", "Utilized MongoDB for efficient storage of attendance records and user data.", "Developed a Python-based desktop application for efficient image resizing and image-to-PDF conversion.", "Implemented image resizing algorithm to reduce pixel count while preserving image quality.", "Utilized the img2pdf library for seamless image-to-PDF conversion.", "Created a user-friendly interface for entering image location, size input, and output format choice."], "durations": ["May 2024", "December 2023", "December 2023", "November 2023"], "companies": ["Cloud IDE", "BuddyPlayer", "Attendance Management System", "Image Resizer"], "locations": ["onsite", "remote", "onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\a954018387_67a4492b5b779.pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Jeet Vyas", "email": "jeetvyas25@gmail.com", "phone": "8969326623", "college": "IIT (BHU), Varanasi", "skills": ["C", "C++", "JavaScript", "Typescript", "SQL", "ReactJS", "NodeJS", "Express", "Redux", "MongoDB", "Stripe", "Git", "Github", "Operating System", "Data Structures &amp; Algorithm", "Classical Machine Learning", "Problem Solving"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["FrontEnd Developer Intern", "Full Stack Development Intern"], "durations": ["2 months", "2 months"], "companies": ["StakeAtlas", "Seisei AI"], "locations": ["onsite", "onsite"]}, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\21135065_Jeet _Vyas_SDE2 (1).pdf"}</t>
+  </si>
+  <si>
+    <t>{"name": "Anjali Wadhe", "email": "anjaliwadhe2016@gmail.com", "phone": "+91-9699215626", "college": "Indian Institute Of Technology, Bombay", "skills": ["Python", "MATLAB", "C++", "HTML/CSS", "Django", "Git/GitHub", "AutoCAD", "MS Office", "ThermoCalc", "Photoshop", "Illustrator", "Figma", "LTSPice", "Arduino IDE"], "graduation_year": 2025, "certification": ["HTML, CSS, and JavaScript from YouAccel Training", "Fine Arts from National Sports Organization(NSO)"], "experience": 0, "Intern_Experience": null, "resume_link": "extracted_resumes\\resumes_20250423_112919\\Resume\\1_Page_Ext (1).pdf"}</t>
+  </si>
+  <si>
     <t>{"name": "Tanisha Kumari", "email": "tanishak2266@gmail.com", "phone": "+91 9608954838", "college": "Indian Institute of Technology (IIT) Bombay", "skills": ["Data Science", "Numpy", "Matplotlib", "MATLAB", "PyTorch", "Pandas", "NLTK", "SQL", "PostgreSQL", "PowerBI", "TensorFlow", "OpenCV"], "graduation_year": 2025, "certification": ["Machine Learning: Unsupervised Learning Recommenders and Reinforcement Learning", "Supervised Machine Learning: Regression and Classifications", "Advanced learning algorithm", "Excel: Excel Skills for Business: Essentials", "Excel: Excel Skills for Business: Intermediate I", "Excel: Excel Skills for Business: Intermediate II", "Excel: Excel Skills for Business: Advanced"], "experience": 0, "Intern_Experience": {"duration_months": 12, "roles": ["Operations Intern", "Data Analyst Intern"], "durations": ["Jan\u201925 - ongoing", "Jun\u201924 - Jul\u201924"], "companies": ["Freedom with AI", "NoQs Digital"], "locations": ["onsite", "remote"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Tanisha_ Kumari.pdf"}</t>
   </si>
   <si>
@@ -113,6 +311,105 @@
   </si>
   <si>
     <t>{"name": "Aman Maurya", "email": "amanmourya295@gmail.com", "phone": "+91 7651867685", "college": "Institute of Engineering and Rural Technology Prayagraj, India", "skills": ["HTML", "CSS", "Tailwind CSS", "Bootstrap", "Shadcn", "JavaScript", "TypeScript", "React", "Next.js", "Node.js", "Django", "Gorilla Mux", "Express", "RESTful APIs", "MongoDB", "PostgreSQL", "SQL", "NoSQL", "Mongoose ODM", "Git", "GitHub", "Python", "C", "C++", "Golang"], "graduation_year": 2025, "certification": [], "experience": 0, "Intern_Experience": {"duration_months": 16, "roles": ["Junior Developer", "MERN Stack Developer Intern"], "durations": ["Oct 2024 - Dec 2024", "Feb 2024 - Jun 2024"], "companies": ["Seetaara | Quick Commerce Platform", "Pixel Stitch | Fashion Design Al SaaS"], "locations": ["Remote", "Remote"]}, "resume_link": "extracted_resumes\\resumes_20250414_190924\\Resumes_15\\Aman_SDE_Fresher-2.pdf"}</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:46</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:39</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:27</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:26</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:25</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:23</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:22</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:12</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:09</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:07</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:05</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:03</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:30:01</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:58</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:56</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:54</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:52</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:50</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:49</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:47</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:44</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:43</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:41</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:39</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:37</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:35</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:34</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:32</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:31</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:29</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:27</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:25</t>
+  </si>
+  <si>
+    <t>2025-04-23 11:29:22</t>
   </si>
   <si>
     <t>2025-04-14 19:10:27</t>
@@ -515,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -534,10 +831,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -545,10 +842,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -556,10 +853,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -567,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -578,10 +875,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -589,10 +886,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -600,10 +897,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -611,10 +908,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -622,10 +919,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -633,10 +930,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -644,10 +941,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -655,10 +952,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -666,10 +963,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -677,10 +974,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -688,10 +985,373 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>32</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
